--- a/data/trans_orig/P1803_2016_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P1803_2016_2023-Edad-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12974</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33697</t>
+          <t>32963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>29021</t>
+          <t>28646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28936</t>
+          <t>29817</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54980</t>
+          <t>55188</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>385766</t>
+          <t>386500</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>406489</t>
+          <t>405723</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>366734</t>
+          <t>367109</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>384158</t>
+          <t>384317</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>760238</t>
+          <t>760030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>786282</t>
+          <t>785401</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>96,34%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17448</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39312</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>29385</t>
+          <t>27772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54806</t>
+          <t>52694</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>49952</t>
+          <t>52154</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84075</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>551184</t>
+          <t>550971</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>573048</t>
+          <t>572831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>508738</t>
+          <t>510850</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>534159</t>
+          <t>535772</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,27%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,79%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1069965</t>
+          <t>1069593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1104088</t>
+          <t>1101886</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>28301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54756</t>
+          <t>55065</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>20812</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42020</t>
+          <t>43232</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>56147</t>
+          <t>53719</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87686</t>
+          <t>87966</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614341</t>
+          <t>614032</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>640018</t>
+          <t>640796</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619366</t>
+          <t>618154</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>641037</t>
+          <t>640574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1242797</t>
+          <t>1242517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1274336</t>
+          <t>1276764</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,96%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20781</t>
+          <t>20531</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44804</t>
+          <t>43595</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24049</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>48333</t>
+          <t>47437</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50306</t>
+          <t>50666</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83838</t>
+          <t>84511</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,12 +1845,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>601244</t>
+          <t>602453</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>625267</t>
+          <t>625517</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>600744</t>
+          <t>601640</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>625028</t>
+          <t>624916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1211287</t>
+          <t>1210614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1244819</t>
+          <t>1244459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,12 +1958,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,09%</t>
         </is>
       </c>
     </row>
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>13987</t>
+          <t>14234</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33746</t>
+          <t>34387</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>20438</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>45031</t>
+          <t>45633</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>40540</t>
+          <t>40671</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>69962</t>
+          <t>71365</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444172</t>
+          <t>443531</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>463931</t>
+          <t>463684</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>451818</t>
+          <t>451216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>476411</t>
+          <t>476336</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>904805</t>
+          <t>903402</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>934227</t>
+          <t>934096</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2980</t>
+          <t>2967</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13904</t>
+          <t>13290</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17159</t>
+          <t>17384</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>39142</t>
+          <t>39381</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2516,12 +2516,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23386</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>48538</t>
+          <t>46709</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,56%</t>
         </is>
       </c>
     </row>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>320426</t>
+          <t>321040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>331350</t>
+          <t>331363</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2574,7 +2574,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>338620</t>
+          <t>338381</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>360603</t>
+          <t>360378</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2629,12 +2629,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>663554</t>
+          <t>665383</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>688706</t>
+          <t>689996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2644,12 +2644,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,9%</t>
         </is>
       </c>
     </row>
@@ -2789,12 +2789,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3289</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12890</t>
+          <t>12487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2804,12 +2804,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7590</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24628</t>
+          <t>24999</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2839,12 +2839,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2859,12 +2859,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13434</t>
+          <t>13640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31836</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2874,12 +2874,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -2902,12 +2902,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>244108</t>
+          <t>244511</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>253709</t>
+          <t>253736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2937,12 +2937,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>375541</t>
+          <t>375170</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>392579</t>
+          <t>391669</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2972,12 +2972,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>625331</t>
+          <t>624410</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>643733</t>
+          <t>643527</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2987,12 +2987,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,92%</t>
         </is>
       </c>
     </row>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>130818</t>
+          <t>132226</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180874</t>
+          <t>181067</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>166982</t>
+          <t>169707</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225840</t>
+          <t>223109</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3182,12 +3182,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>312431</t>
+          <t>315049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>390129</t>
+          <t>391061</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3213476</t>
+          <t>3213283</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3263532</t>
+          <t>3262124</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3318702</t>
+          <t>3321433</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3377560</t>
+          <t>3374835</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>6548763</t>
+          <t>6547831</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6626461</t>
+          <t>6623843</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -3705,32 +3705,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>22952</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>10493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39418</t>
+          <t>40787</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3740,32 +3740,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>9622</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28864</t>
+          <t>33842</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3775,32 +3775,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>34710</t>
+          <t>41168</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19508</t>
+          <t>25046</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57965</t>
+          <t>64094</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,32%</t>
         </is>
       </c>
     </row>
@@ -3818,32 +3818,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>380611</t>
+          <t>384841</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>360569</t>
+          <t>367006</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>392536</t>
+          <t>397300</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3853,32 +3853,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>297866</t>
+          <t>344296</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>284336</t>
+          <t>328670</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>305511</t>
+          <t>352890</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3888,32 +3888,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>678477</t>
+          <t>729137</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>655222</t>
+          <t>706211</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>693679</t>
+          <t>745259</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -3931,17 +3931,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3966,17 +3966,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4001,17 +4001,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4048,32 +4048,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>35387</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>22683</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49531</t>
+          <t>52889</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4083,32 +4083,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>50801</t>
+          <t>48639</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32075</t>
+          <t>36037</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70011</t>
+          <t>64568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4118,32 +4118,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>84335</t>
+          <t>84027</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60312</t>
+          <t>65071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108383</t>
+          <t>106502</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,89%</t>
         </is>
       </c>
     </row>
@@ -4161,32 +4161,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>390013</t>
+          <t>441503</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>374016</t>
+          <t>424001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401711</t>
+          <t>454207</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4196,32 +4196,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>460703</t>
+          <t>452444</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>441493</t>
+          <t>436515</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>479429</t>
+          <t>465046</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4231,32 +4231,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>850716</t>
+          <t>893946</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>826668</t>
+          <t>871471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>874739</t>
+          <t>912902</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,35%</t>
         </is>
       </c>
     </row>
@@ -4274,17 +4274,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>423547</t>
+          <t>476890</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4309,17 +4309,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>511504</t>
+          <t>501083</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4344,17 +4344,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>935051</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4391,32 +4391,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>69512</t>
+          <t>69075</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>55404</t>
+          <t>52803</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86787</t>
+          <t>85463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4426,67 +4426,67 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>59628</t>
+          <t>62127</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48779</t>
+          <t>49569</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72622</t>
+          <t>76483</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>12,29%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>131203</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>111791</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>154691</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>10,56%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>8,99%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>13,39%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>129140</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>110892</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>150867</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>11,97%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>10,28%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -4504,32 +4504,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>466826</t>
+          <t>551762</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>449551</t>
+          <t>535374</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480934</t>
+          <t>568034</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4539,67 +4539,67 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>482840</t>
+          <t>560012</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>469846</t>
+          <t>545656</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>493689</t>
+          <t>572570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>1245</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>1111773</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>1088285</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>1131185</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>89,44%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>87,55%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>91,01%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>1245</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>949666</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>927939</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>967914</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>88,03%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>89,72%</t>
         </is>
       </c>
     </row>
@@ -4617,17 +4617,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>536338</t>
+          <t>620837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4652,17 +4652,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542468</t>
+          <t>622139</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4687,17 +4687,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1078806</t>
+          <t>1242976</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4734,32 +4734,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>314059</t>
+          <t>72711</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>88961</t>
+          <t>57558</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>649477</t>
+          <t>92393</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4769,32 +4769,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>76588</t>
+          <t>83439</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>61238</t>
+          <t>70200</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90100</t>
+          <t>96921</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4804,32 +4804,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>390647</t>
+          <t>156149</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161706</t>
+          <t>135083</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>789746</t>
+          <t>177587</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>12,35%</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4847,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>573727</t>
+          <t>627906</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>238309</t>
+          <t>608224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>798825</t>
+          <t>643059</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>86,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4882,32 +4882,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>636293</t>
+          <t>653447</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>622781</t>
+          <t>639965</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>651643</t>
+          <t>666686</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>89,26%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>86,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4917,32 +4917,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1210020</t>
+          <t>1281355</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>810921</t>
+          <t>1259917</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1438961</t>
+          <t>1302421</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>75,59%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -4960,17 +4960,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4995,17 +4995,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>712881</t>
+          <t>736886</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1600667</t>
+          <t>1437504</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5077,32 +5077,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34677</t>
+          <t>34747</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>58954</t>
+          <t>58890</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5112,32 +5112,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>72436</t>
+          <t>79423</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>62048</t>
+          <t>66619</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>84481</t>
+          <t>91456</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5147,32 +5147,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>117893</t>
+          <t>125400</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>102973</t>
+          <t>109424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>136970</t>
+          <t>143665</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -5190,32 +5190,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>515778</t>
+          <t>563368</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>502280</t>
+          <t>550456</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>526557</t>
+          <t>574599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5225,32 +5225,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>474288</t>
+          <t>528209</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>462243</t>
+          <t>516176</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>484676</t>
+          <t>541013</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5260,32 +5260,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>990065</t>
+          <t>1091578</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>970988</t>
+          <t>1073313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1004985</t>
+          <t>1107554</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,01%</t>
         </is>
       </c>
     </row>
@@ -5303,17 +5303,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5338,17 +5338,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>546724</t>
+          <t>607632</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>546724</t>
+          <t>607632</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>546724</t>
+          <t>607632</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5373,17 +5373,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1107958</t>
+          <t>1216978</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1107958</t>
+          <t>1216978</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1107958</t>
+          <t>1216978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5420,32 +5420,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>23682</t>
+          <t>26002</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16564</t>
+          <t>19120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32296</t>
+          <t>35603</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5455,32 +5455,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43495</t>
+          <t>47937</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>39709</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>70424</t>
+          <t>58224</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5490,32 +5490,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>67177</t>
+          <t>73939</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>35615</t>
+          <t>61812</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>89647</t>
+          <t>89009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,52%</t>
         </is>
       </c>
     </row>
@@ -5533,32 +5533,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>344483</t>
+          <t>381078</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>335869</t>
+          <t>371477</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>351601</t>
+          <t>387960</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5568,32 +5568,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>564873</t>
+          <t>391229</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>537944</t>
+          <t>380942</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>590433</t>
+          <t>399457</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>90,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5603,32 +5603,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>909356</t>
+          <t>772307</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>886886</t>
+          <t>757237</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>940918</t>
+          <t>784434</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>92,7%</t>
         </is>
       </c>
     </row>
@@ -5646,17 +5646,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5681,17 +5681,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5716,17 +5716,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5763,32 +5763,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8888</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5033</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>16581</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5798,32 +5798,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>27609</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20390</t>
+          <t>23437</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34813</t>
+          <t>39767</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5833,32 +5833,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>36497</t>
+          <t>40917</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29284</t>
+          <t>33262</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>45641</t>
+          <t>52402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -5876,32 +5876,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>273871</t>
+          <t>300306</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>268063</t>
+          <t>293617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277726</t>
+          <t>304517</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5911,32 +5911,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>397656</t>
+          <t>432988</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>390452</t>
+          <t>424246</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>404875</t>
+          <t>440576</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5946,32 +5946,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>671527</t>
+          <t>733294</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>662383</t>
+          <t>721809</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>678740</t>
+          <t>740949</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,7%</t>
         </is>
       </c>
     </row>
@@ -5989,17 +5989,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6024,17 +6024,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>425265</t>
+          <t>464013</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6059,17 +6059,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708024</t>
+          <t>774211</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6106,32 +6106,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>514507</t>
+          <t>281996</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>278006</t>
+          <t>249779</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1172526</t>
+          <t>322394</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,89%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6141,32 +6141,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>345891</t>
+          <t>370807</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>283016</t>
+          <t>337119</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>387944</t>
+          <t>401514</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6176,32 +6176,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>860399</t>
+          <t>652803</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>619385</t>
+          <t>610512</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1663521</t>
+          <t>704185</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>9,69%</t>
         </is>
       </c>
     </row>
@@ -6219,32 +6219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>2945310</t>
+          <t>3250766</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2287291</t>
+          <t>3210368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3181811</t>
+          <t>3282983</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6254,32 +6254,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>3314519</t>
+          <t>3362624</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3272466</t>
+          <t>3331917</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3377394</t>
+          <t>3396312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6289,32 +6289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6259828</t>
+          <t>6613390</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5456706</t>
+          <t>6562008</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6500842</t>
+          <t>6655681</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>90,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,6%</t>
         </is>
       </c>
     </row>
@@ -6332,17 +6332,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6367,17 +6367,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3660410</t>
+          <t>3733431</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6402,17 +6402,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>7120227</t>
+          <t>7266193</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
